--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Chen 98.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Chen 98.xlsx
@@ -1760,10 +1760,10 @@
         <v>15.81</v>
       </c>
       <c r="F16" t="n">
-        <v>20.655</v>
+        <v>20.65</v>
       </c>
       <c r="G16" t="n">
-        <v>8.32</v>
+        <v>8.31</v>
       </c>
       <c r="H16" t="n">
         <v>12.6</v>
@@ -1775,25 +1775,25 @@
         <v>19.03</v>
       </c>
       <c r="K16" t="n">
-        <v>11.372</v>
+        <v>11.37</v>
       </c>
       <c r="L16" t="n">
-        <v>16.779</v>
+        <v>16.78</v>
       </c>
       <c r="M16" t="n">
-        <v>11.744</v>
+        <v>11.74</v>
       </c>
       <c r="N16" t="n">
-        <v>16.454</v>
+        <v>16.45</v>
       </c>
       <c r="O16" t="n">
-        <v>14.075</v>
+        <v>14.07</v>
       </c>
       <c r="P16" t="n">
-        <v>14.099</v>
+        <v>14.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.087</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="17">
@@ -1806,25 +1806,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="D17" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="E17" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="F17" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G17" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="H17" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="I17" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="J17" t="n">
         <v>18.36</v>
@@ -1833,22 +1833,22 @@
         <v>9.59</v>
       </c>
       <c r="L17" t="n">
-        <v>15.698</v>
+        <v>15.7</v>
       </c>
       <c r="M17" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>15.308</v>
+        <v>15.31</v>
       </c>
       <c r="O17" t="n">
-        <v>12.644</v>
+        <v>12.64</v>
       </c>
       <c r="P17" t="n">
-        <v>12.599</v>
+        <v>12.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.622</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="18">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="D18" t="n">
         <v>10.35</v>
@@ -1870,10 +1870,10 @@
         <v>14.66</v>
       </c>
       <c r="F18" t="n">
-        <v>20.655</v>
+        <v>20.66</v>
       </c>
       <c r="G18" t="n">
-        <v>6.835</v>
+        <v>6.83</v>
       </c>
       <c r="H18" t="n">
         <v>10.35</v>
@@ -1885,25 +1885,25 @@
         <v>18.63</v>
       </c>
       <c r="K18" t="n">
-        <v>9.332000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="L18" t="n">
-        <v>15.859</v>
+        <v>15.86</v>
       </c>
       <c r="M18" t="n">
-        <v>9.647</v>
+        <v>9.65</v>
       </c>
       <c r="N18" t="n">
-        <v>15.454</v>
+        <v>15.45</v>
       </c>
       <c r="O18" t="n">
-        <v>12.596</v>
+        <v>12.6</v>
       </c>
       <c r="P18" t="n">
         <v>12.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.573</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="19">
@@ -1919,22 +1919,22 @@
         <v>4.45</v>
       </c>
       <c r="D19" t="n">
-        <v>8.324999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E19" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F19" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G19" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H19" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I19" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J19" t="n">
         <v>17.96</v>
@@ -1943,22 +1943,22 @@
         <v>7.55</v>
       </c>
       <c r="L19" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M19" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N19" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O19" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P19" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.107</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="20">
@@ -1974,22 +1974,22 @@
         <v>4.45</v>
       </c>
       <c r="D20" t="n">
-        <v>8.324999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E20" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F20" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G20" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H20" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I20" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J20" t="n">
         <v>17.96</v>
@@ -1998,22 +1998,22 @@
         <v>7.55</v>
       </c>
       <c r="L20" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M20" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N20" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O20" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P20" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.107</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="21">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D21" t="n">
         <v>9.09</v>
@@ -2038,7 +2038,7 @@
         <v>17.34</v>
       </c>
       <c r="G21" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H21" t="n">
         <v>9.09</v>
@@ -2050,25 +2050,25 @@
         <v>15.83</v>
       </c>
       <c r="K21" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L21" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M21" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N21" t="n">
         <v>13.35</v>
       </c>
       <c r="O21" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P21" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="22">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D22" t="n">
         <v>9.09</v>
@@ -2093,7 +2093,7 @@
         <v>17.34</v>
       </c>
       <c r="G22" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H22" t="n">
         <v>9.09</v>
@@ -2105,25 +2105,25 @@
         <v>15.83</v>
       </c>
       <c r="K22" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L22" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M22" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N22" t="n">
         <v>13.35</v>
       </c>
       <c r="O22" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P22" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="23">
@@ -2136,46 +2136,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.015</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>7.425</v>
+        <v>7.43</v>
       </c>
       <c r="E23" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="F23" t="n">
-        <v>19.965</v>
+        <v>19.96</v>
       </c>
       <c r="G23" t="n">
         <v>5.08</v>
       </c>
       <c r="H23" t="n">
-        <v>7.425</v>
+        <v>7.42</v>
       </c>
       <c r="I23" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="J23" t="n">
         <v>17.49</v>
       </c>
       <c r="K23" t="n">
-        <v>6.743</v>
+        <v>6.74</v>
       </c>
       <c r="L23" t="n">
-        <v>14.157</v>
+        <v>14.16</v>
       </c>
       <c r="M23" t="n">
-        <v>6.956</v>
+        <v>6.96</v>
       </c>
       <c r="N23" t="n">
-        <v>13.662</v>
+        <v>13.67</v>
       </c>
       <c r="O23" t="n">
         <v>10.45</v>
       </c>
       <c r="P23" t="n">
-        <v>10.309</v>
+        <v>10.31</v>
       </c>
       <c r="Q23" t="n">
         <v>10.38</v>
@@ -2191,49 +2191,49 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D24" t="n">
-        <v>6.015</v>
+        <v>6.02</v>
       </c>
       <c r="E24" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="F24" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G24" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H24" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I24" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="J24" t="n">
         <v>14.43</v>
       </c>
       <c r="K24" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L24" t="n">
-        <v>11.847</v>
+        <v>11.84</v>
       </c>
       <c r="M24" t="n">
-        <v>5.437</v>
+        <v>5.44</v>
       </c>
       <c r="N24" t="n">
         <v>11.49</v>
       </c>
       <c r="O24" t="n">
-        <v>8.548999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="25">
@@ -2246,49 +2246,49 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D25" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E25" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="F25" t="n">
-        <v>14.025</v>
+        <v>14.03</v>
       </c>
       <c r="G25" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H25" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I25" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="J25" t="n">
         <v>12.43</v>
       </c>
       <c r="K25" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>10.065</v>
+        <v>10.06</v>
       </c>
       <c r="M25" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N25" t="n">
-        <v>9.746</v>
+        <v>9.74</v>
       </c>
       <c r="O25" t="n">
         <v>6.93</v>
       </c>
       <c r="P25" t="n">
-        <v>6.837</v>
+        <v>6.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.883</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="28">
@@ -2372,25 +2372,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D31" t="n">
-        <v>13.325</v>
+        <v>13.33</v>
       </c>
       <c r="E31" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F31" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G31" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I31" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J31" t="n">
         <v>22.96</v>
@@ -2399,22 +2399,22 @@
         <v>12.12</v>
       </c>
       <c r="L31" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M31" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N31" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O31" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P31" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="32">
@@ -2427,25 +2427,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D32" t="n">
-        <v>13.325</v>
+        <v>13.33</v>
       </c>
       <c r="E32" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F32" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G32" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I32" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J32" t="n">
         <v>22.96</v>
@@ -2454,22 +2454,22 @@
         <v>12.12</v>
       </c>
       <c r="L32" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M32" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N32" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O32" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P32" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="33">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D33" t="n">
         <v>11.84</v>
@@ -2506,25 +2506,25 @@
         <v>20.43</v>
       </c>
       <c r="K33" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L33" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M33" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N33" t="n">
         <v>17.35</v>
       </c>
       <c r="O33" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P33" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="34">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D34" t="n">
         <v>11.84</v>
@@ -2561,25 +2561,25 @@
         <v>20.43</v>
       </c>
       <c r="K34" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L34" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M34" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N34" t="n">
         <v>17.35</v>
       </c>
       <c r="O34" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P34" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="35">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D35" t="n">
         <v>11.84</v>
@@ -2616,25 +2616,25 @@
         <v>20.43</v>
       </c>
       <c r="K35" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L35" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M35" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N35" t="n">
         <v>17.35</v>
       </c>
       <c r="O35" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P35" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q35" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="36">
@@ -2647,49 +2647,49 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D36" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E36" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F36" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G36" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H36" t="n">
-        <v>11.015</v>
+        <v>11.02</v>
       </c>
       <c r="I36" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J36" t="n">
         <v>19.43</v>
       </c>
       <c r="K36" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L36" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M36" t="n">
-        <v>10.127</v>
+        <v>10.13</v>
       </c>
       <c r="N36" t="n">
         <v>16.49</v>
       </c>
       <c r="O36" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P36" t="n">
-        <v>13.308</v>
+        <v>13.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="37">
@@ -2702,49 +2702,49 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D37" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E37" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F37" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G37" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H37" t="n">
-        <v>11.015</v>
+        <v>11.02</v>
       </c>
       <c r="I37" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J37" t="n">
         <v>19.43</v>
       </c>
       <c r="K37" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L37" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M37" t="n">
-        <v>10.127</v>
+        <v>10.13</v>
       </c>
       <c r="N37" t="n">
         <v>16.49</v>
       </c>
       <c r="O37" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P37" t="n">
-        <v>13.308</v>
+        <v>13.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="38">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D38" t="n">
         <v>9.890000000000001</v>
@@ -2766,10 +2766,10 @@
         <v>15.18</v>
       </c>
       <c r="F38" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G38" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H38" t="n">
         <v>9.890000000000001</v>
@@ -2781,25 +2781,25 @@
         <v>19.23</v>
       </c>
       <c r="K38" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L38" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M38" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>15.99</v>
       </c>
       <c r="O38" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P38" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="39">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D39" t="n">
         <v>9.890000000000001</v>
@@ -2821,10 +2821,10 @@
         <v>15.18</v>
       </c>
       <c r="F39" t="n">
-        <v>21.215</v>
+        <v>21.22</v>
       </c>
       <c r="G39" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H39" t="n">
         <v>9.890000000000001</v>
@@ -2836,25 +2836,25 @@
         <v>19.23</v>
       </c>
       <c r="K39" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L39" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M39" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>15.99</v>
       </c>
       <c r="O39" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P39" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="40">
@@ -2867,49 +2867,49 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D40" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="E40" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="F40" t="n">
-        <v>16.775</v>
+        <v>16.77</v>
       </c>
       <c r="G40" t="n">
-        <v>1.965</v>
+        <v>1.96</v>
       </c>
       <c r="H40" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="I40" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="J40" t="n">
         <v>15.03</v>
       </c>
       <c r="K40" t="n">
-        <v>4.675</v>
+        <v>4.68</v>
       </c>
       <c r="L40" t="n">
-        <v>12.375</v>
+        <v>12.38</v>
       </c>
       <c r="M40" t="n">
-        <v>4.837</v>
+        <v>4.84</v>
       </c>
       <c r="N40" t="n">
-        <v>12.026</v>
+        <v>12.03</v>
       </c>
       <c r="O40" t="n">
-        <v>8.525</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P40" t="n">
-        <v>8.430999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="Q40" t="n">
-        <v>8.478</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="43">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.825</v>
+        <v>4.81</v>
       </c>
       <c r="D46" t="n">
         <v>9.449999999999999</v>
@@ -3002,10 +3002,10 @@
         <v>13.97</v>
       </c>
       <c r="F46" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G46" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="H46" t="n">
         <v>9.449999999999999</v>
@@ -3017,25 +3017,25 @@
         <v>18.16</v>
       </c>
       <c r="K46" t="n">
-        <v>8.525</v>
+        <v>8.52</v>
       </c>
       <c r="L46" t="n">
-        <v>15.238</v>
+        <v>15.24</v>
       </c>
       <c r="M46" t="n">
         <v>8.81</v>
       </c>
       <c r="N46" t="n">
-        <v>14.808</v>
+        <v>14.81</v>
       </c>
       <c r="O46" t="n">
-        <v>11.881</v>
+        <v>11.88</v>
       </c>
       <c r="P46" t="n">
-        <v>11.809</v>
+        <v>11.81</v>
       </c>
       <c r="Q46" t="n">
-        <v>11.845</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="47">
@@ -3048,49 +3048,49 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5.045</v>
+        <v>5.05</v>
       </c>
       <c r="D47" t="n">
-        <v>9.914999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="E47" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="F47" t="n">
-        <v>18.465</v>
+        <v>18.46</v>
       </c>
       <c r="G47" t="n">
-        <v>6.429</v>
+        <v>6.42</v>
       </c>
       <c r="H47" t="n">
-        <v>9.914999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="I47" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="J47" t="n">
         <v>16.83</v>
       </c>
       <c r="K47" t="n">
-        <v>8.941000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="L47" t="n">
-        <v>14.537</v>
+        <v>14.54</v>
       </c>
       <c r="M47" t="n">
-        <v>9.218</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>14.21</v>
       </c>
       <c r="O47" t="n">
-        <v>11.739</v>
+        <v>11.74</v>
       </c>
       <c r="P47" t="n">
-        <v>11.714</v>
+        <v>11.71</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.727</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="48">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D48" t="n">
         <v>8.789999999999999</v>
@@ -3112,10 +3112,10 @@
         <v>12.98</v>
       </c>
       <c r="F48" t="n">
-        <v>18.465</v>
+        <v>18.47</v>
       </c>
       <c r="G48" t="n">
-        <v>5.529</v>
+        <v>5.52</v>
       </c>
       <c r="H48" t="n">
         <v>8.789999999999999</v>
@@ -3127,22 +3127,22 @@
         <v>16.63</v>
       </c>
       <c r="K48" t="n">
-        <v>7.876</v>
+        <v>7.87</v>
       </c>
       <c r="L48" t="n">
-        <v>14.077</v>
+        <v>14.08</v>
       </c>
       <c r="M48" t="n">
-        <v>8.138</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N48" t="n">
         <v>13.71</v>
       </c>
       <c r="O48" t="n">
-        <v>10.976</v>
+        <v>10.97</v>
       </c>
       <c r="P48" t="n">
-        <v>10.924</v>
+        <v>10.93</v>
       </c>
       <c r="Q48" t="n">
         <v>10.95</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.495</v>
+        <v>4.49</v>
       </c>
       <c r="D49" t="n">
         <v>9.09</v>
@@ -3170,7 +3170,7 @@
         <v>17.34</v>
       </c>
       <c r="G49" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H49" t="n">
         <v>9.09</v>
@@ -3182,25 +3182,25 @@
         <v>15.83</v>
       </c>
       <c r="K49" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L49" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M49" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N49" t="n">
         <v>13.35</v>
       </c>
       <c r="O49" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P49" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="50">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D50" t="n">
         <v>7.14</v>
@@ -3222,10 +3222,10 @@
         <v>11.33</v>
       </c>
       <c r="F50" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G50" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H50" t="n">
         <v>7.14</v>
@@ -3237,25 +3237,25 @@
         <v>14.63</v>
       </c>
       <c r="K50" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L50" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M50" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N50" t="n">
         <v>11.99</v>
       </c>
       <c r="O50" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P50" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q50" t="n">
-        <v>9.244</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="51">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D51" t="n">
         <v>7.14</v>
@@ -3277,10 +3277,10 @@
         <v>11.33</v>
       </c>
       <c r="F51" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G51" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H51" t="n">
         <v>7.14</v>
@@ -3292,25 +3292,25 @@
         <v>14.63</v>
       </c>
       <c r="K51" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L51" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M51" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N51" t="n">
         <v>11.99</v>
       </c>
       <c r="O51" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P51" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>9.244</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="52">
@@ -3323,49 +3323,49 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D52" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E52" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F52" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G52" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H52" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I52" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J52" t="n">
         <v>14.43</v>
       </c>
       <c r="K52" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L52" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M52" t="n">
-        <v>5.437</v>
+        <v>5.44</v>
       </c>
       <c r="N52" t="n">
         <v>11.49</v>
       </c>
       <c r="O52" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q52" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="53">
@@ -3378,49 +3378,49 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D53" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E53" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F53" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G53" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H53" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I53" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J53" t="n">
         <v>14.43</v>
       </c>
       <c r="K53" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L53" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M53" t="n">
-        <v>5.437</v>
+        <v>5.44</v>
       </c>
       <c r="N53" t="n">
         <v>11.49</v>
       </c>
       <c r="O53" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="54">
@@ -3433,49 +3433,49 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D54" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E54" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F54" t="n">
-        <v>14.025</v>
+        <v>14.02</v>
       </c>
       <c r="G54" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H54" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I54" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="J54" t="n">
         <v>12.43</v>
       </c>
       <c r="K54" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L54" t="n">
-        <v>10.065</v>
+        <v>10.07</v>
       </c>
       <c r="M54" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N54" t="n">
-        <v>9.746</v>
+        <v>9.75</v>
       </c>
       <c r="O54" t="n">
         <v>6.93</v>
       </c>
       <c r="P54" t="n">
-        <v>6.837</v>
+        <v>6.84</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.883</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="55">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="D55" t="n">
         <v>3.63</v>
@@ -3500,7 +3500,7 @@
         <v>12.9</v>
       </c>
       <c r="G55" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="H55" t="n">
         <v>3.63</v>
@@ -3512,22 +3512,22 @@
         <v>11.43</v>
       </c>
       <c r="K55" t="n">
-        <v>3.025</v>
+        <v>3.02</v>
       </c>
       <c r="L55" t="n">
         <v>9.18</v>
       </c>
       <c r="M55" t="n">
-        <v>3.109</v>
+        <v>3.11</v>
       </c>
       <c r="N55" t="n">
-        <v>8.885999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>6.103</v>
+        <v>6.1</v>
       </c>
       <c r="P55" t="n">
-        <v>5.997</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
         <v>6.05</v>
@@ -3562,10 +3562,10 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
@@ -3576,47 +3576,47 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0.948</v>
+        <v>0.95</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.953</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="C63" t="n">
-        <v>0.948</v>
+        <v>0.95</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
       <c r="H63" t="n">
-        <v>0.953</v>
+        <v>0.95</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3635,7 +3635,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>0.967</v>
+        <v>0.97</v>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>0.966</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="66">
@@ -3660,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.907</v>
+        <v>0.91</v>
       </c>
       <c r="G66" t="n">
         <v>0.9399999999999999</v>
@@ -3669,24 +3669,24 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.906</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>0.967</v>
+        <v>0.97</v>
       </c>
       <c r="C67" t="n">
-        <v>0.907</v>
+        <v>0.91</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.966</v>
+        <v>0.97</v>
       </c>
       <c r="H67" t="n">
-        <v>0.906</v>
+        <v>0.91</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         <v>0.8</v>
       </c>
       <c r="D69" t="n">
-        <v>0.956</v>
+        <v>0.96</v>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="I69" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="70">
@@ -3730,33 +3730,33 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0.844</v>
+        <v>0.84</v>
       </c>
       <c r="G70" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.842</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>0.956</v>
+        <v>0.96</v>
       </c>
       <c r="C71" t="n">
-        <v>0.844</v>
+        <v>0.84</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
       <c r="H71" t="n">
-        <v>0.842</v>
+        <v>0.84</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -3772,10 +3772,10 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.843</v>
+        <v>0.84</v>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
@@ -3786,47 +3786,47 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>0.843</v>
+        <v>0.84</v>
       </c>
       <c r="C75" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="H75" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -3842,10 +3842,10 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="D77" t="n">
-        <v>0.909</v>
+        <v>0.91</v>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
@@ -3856,47 +3856,47 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="I77" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>0.909</v>
+        <v>0.91</v>
       </c>
       <c r="C79" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="H79" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -3912,10 +3912,10 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="D81" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
@@ -3929,18 +3929,18 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>0.847</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="G82" t="n">
         <v>0.87</v>
@@ -3949,24 +3949,24 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="C83" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.847</v>
+        <v>0.85</v>
       </c>
       <c r="H83" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -3982,10 +3982,10 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="D85" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
@@ -3999,18 +3999,18 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="G86" t="n">
         <v>0.87</v>
@@ -4019,24 +4019,24 @@
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="C87" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
       <c r="H87" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -4052,10 +4052,10 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="D89" t="n">
-        <v>0.928</v>
+        <v>0.93</v>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
@@ -4066,47 +4066,47 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.973</v>
+        <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0.927</v>
+        <v>0.93</v>
       </c>
       <c r="G90" t="n">
-        <v>0.973</v>
+        <v>0.97</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>0.928</v>
+        <v>0.93</v>
       </c>
       <c r="C91" t="n">
-        <v>0.927</v>
+        <v>0.93</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -4122,10 +4122,10 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>0.909</v>
+        <v>0.91</v>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
@@ -4136,47 +4136,47 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.927</v>
+        <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0.844</v>
+        <v>0.84</v>
       </c>
       <c r="G94" t="n">
-        <v>0.927</v>
+        <v>0.93</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0.842</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>0.909</v>
+        <v>0.91</v>
       </c>
       <c r="C95" t="n">
-        <v>0.844</v>
+        <v>0.84</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="H95" t="n">
-        <v>0.842</v>
+        <v>0.84</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -4192,10 +4192,10 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="D97" t="n">
-        <v>0.908</v>
+        <v>0.91</v>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
@@ -4206,47 +4206,47 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="I97" t="n">
-        <v>0.905</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0.915</v>
+        <v>0.92</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.913</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>0.908</v>
+        <v>0.91</v>
       </c>
       <c r="C99" t="n">
-        <v>0.915</v>
+        <v>0.92</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.905</v>
+        <v>0.91</v>
       </c>
       <c r="H99" t="n">
-        <v>0.913</v>
+        <v>0.91</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.927474</v>
+        <v>0.93</v>
       </c>
       <c r="C105" t="n">
-        <v>0.943871</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>0.931993</v>
+        <v>0.93</v>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.924852</v>
+        <v>0.92</v>
       </c>
       <c r="H105" t="n">
-        <v>0.945728</v>
+        <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9316719999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="106">
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.953699</v>
+        <v>0.95</v>
       </c>
       <c r="C106" t="n">
-        <v>0.92382</v>
+        <v>0.92</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9372779999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
@@ -4322,13 +4322,13 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.953131</v>
+        <v>0.95</v>
       </c>
       <c r="H106" t="n">
-        <v>0.923271</v>
+        <v>0.92</v>
       </c>
       <c r="I106" t="n">
-        <v>0.936122</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.878185</v>
+        <v>0.88</v>
       </c>
       <c r="C107" t="n">
-        <v>0.822229</v>
+        <v>0.82</v>
       </c>
       <c r="D107" t="n">
-        <v>0.900138</v>
+        <v>0.9</v>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
@@ -4352,13 +4352,13 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.8704809999999999</v>
+        <v>0.87</v>
       </c>
       <c r="H107" t="n">
-        <v>0.81697</v>
+        <v>0.82</v>
       </c>
       <c r="I107" t="n">
-        <v>0.895817</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="108">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.892705</v>
+        <v>0.89</v>
       </c>
       <c r="C108" t="n">
-        <v>0.863937</v>
+        <v>0.86</v>
       </c>
       <c r="D108" t="n">
-        <v>0.814179</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F108" s="13" t="inlineStr">
         <is>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.89073</v>
+        <v>0.89</v>
       </c>
       <c r="H108" t="n">
-        <v>0.861986</v>
+        <v>0.86</v>
       </c>
       <c r="I108" t="n">
-        <v>0.810203</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.866283</v>
+        <v>0.87</v>
       </c>
       <c r="C109" t="n">
-        <v>0.778126</v>
+        <v>0.78</v>
       </c>
       <c r="D109" t="n">
-        <v>0.820723</v>
+        <v>0.82</v>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.8667280000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H109" t="n">
-        <v>0.775607</v>
+        <v>0.78</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8245749999999999</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="110">
@@ -4428,13 +4428,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.860752</v>
+        <v>0.86</v>
       </c>
       <c r="C110" t="n">
-        <v>0.795313</v>
+        <v>0.8</v>
       </c>
       <c r="D110" t="n">
-        <v>0.786942</v>
+        <v>0.79</v>
       </c>
       <c r="F110" s="13" t="inlineStr">
         <is>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.858401</v>
+        <v>0.86</v>
       </c>
       <c r="H110" t="n">
-        <v>0.793382</v>
+        <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>0.78182</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="111">
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.892705</v>
+        <v>0.89</v>
       </c>
       <c r="C111" t="n">
-        <v>0.827267</v>
+        <v>0.83</v>
       </c>
       <c r="D111" t="n">
-        <v>0.850849</v>
+        <v>0.85</v>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.89073</v>
+        <v>0.89</v>
       </c>
       <c r="H111" t="n">
-        <v>0.825711</v>
+        <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>0.846479</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="112">
@@ -4488,13 +4488,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.951353</v>
+        <v>0.95</v>
       </c>
       <c r="C112" t="n">
-        <v>0.950711</v>
+        <v>0.95</v>
       </c>
       <c r="D112" t="n">
-        <v>0.927548</v>
+        <v>0.93</v>
       </c>
       <c r="F112" s="13" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.950958</v>
+        <v>0.95</v>
       </c>
       <c r="H112" t="n">
-        <v>0.953427</v>
+        <v>0.95</v>
       </c>
       <c r="I112" t="n">
-        <v>0.93145</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="113">
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.922091</v>
+        <v>0.92</v>
       </c>
       <c r="C113" t="n">
-        <v>0.889742</v>
+        <v>0.89</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8765309999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F113" s="13" t="inlineStr">
         <is>
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.921153</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="n">
-        <v>0.884458</v>
+        <v>0.88</v>
       </c>
       <c r="I113" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="114">
@@ -4548,13 +4548,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.866036</v>
+        <v>0.87</v>
       </c>
       <c r="C114" t="n">
-        <v>0.869493</v>
+        <v>0.87</v>
       </c>
       <c r="D114" t="n">
-        <v>0.911843</v>
+        <v>0.91</v>
       </c>
       <c r="F114" s="13" t="inlineStr">
         <is>
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.861448</v>
+        <v>0.86</v>
       </c>
       <c r="H114" t="n">
-        <v>0.865192</v>
+        <v>0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>0.90888</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="117">
@@ -4585,13 +4585,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.926163</v>
+        <v>0.93</v>
       </c>
       <c r="C119" t="n">
-        <v>0.9447990000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>0.931833</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="120">
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.953415</v>
+        <v>0.95</v>
       </c>
       <c r="C120" t="n">
-        <v>0.923546</v>
+        <v>0.92</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9367</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -4617,13 +4617,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.874333</v>
+        <v>0.87</v>
       </c>
       <c r="C121" t="n">
-        <v>0.819599</v>
+        <v>0.82</v>
       </c>
       <c r="D121" t="n">
-        <v>0.8979780000000001</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122">
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.891718</v>
+        <v>0.89</v>
       </c>
       <c r="C122" t="n">
-        <v>0.862962</v>
+        <v>0.86</v>
       </c>
       <c r="D122" t="n">
-        <v>0.812191</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -4649,13 +4649,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.866505</v>
+        <v>0.87</v>
       </c>
       <c r="C123" t="n">
-        <v>0.776867</v>
+        <v>0.78</v>
       </c>
       <c r="D123" t="n">
-        <v>0.822649</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="124">
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.859576</v>
+        <v>0.86</v>
       </c>
       <c r="C124" t="n">
-        <v>0.7943480000000001</v>
+        <v>0.79</v>
       </c>
       <c r="D124" t="n">
-        <v>0.784381</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="125">
@@ -4681,13 +4681,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.891718</v>
+        <v>0.89</v>
       </c>
       <c r="C125" t="n">
-        <v>0.826489</v>
+        <v>0.83</v>
       </c>
       <c r="D125" t="n">
-        <v>0.848664</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="126">
@@ -4697,13 +4697,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.951156</v>
+        <v>0.95</v>
       </c>
       <c r="C126" t="n">
-        <v>0.9520690000000001</v>
+        <v>0.95</v>
       </c>
       <c r="D126" t="n">
-        <v>0.929499</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="127">
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.9216220000000001</v>
+        <v>0.92</v>
       </c>
       <c r="C127" t="n">
-        <v>0.8871</v>
+        <v>0.89</v>
       </c>
       <c r="D127" t="n">
-        <v>0.877766</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="128">
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.863742</v>
+        <v>0.86</v>
       </c>
       <c r="C128" t="n">
-        <v>0.8673419999999999</v>
+        <v>0.87</v>
       </c>
       <c r="D128" t="n">
-        <v>0.910362</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="131">
@@ -4752,13 +4752,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.330443</v>
+        <v>0.33</v>
       </c>
       <c r="C133" t="n">
-        <v>0.337092</v>
+        <v>0.34</v>
       </c>
       <c r="D133" t="n">
-        <v>0.332466</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="134">
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.338852</v>
+        <v>0.34</v>
       </c>
       <c r="C134" t="n">
-        <v>0.328236</v>
+        <v>0.33</v>
       </c>
       <c r="D134" t="n">
-        <v>0.332911</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="135">
@@ -4784,13 +4784,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.337332</v>
+        <v>0.34</v>
       </c>
       <c r="C135" t="n">
-        <v>0.316214</v>
+        <v>0.32</v>
       </c>
       <c r="D135" t="n">
-        <v>0.346454</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="136">
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.347395</v>
+        <v>0.35</v>
       </c>
       <c r="C136" t="n">
-        <v>0.336192</v>
+        <v>0.34</v>
       </c>
       <c r="D136" t="n">
-        <v>0.316413</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="137">
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.351378</v>
+        <v>0.35</v>
       </c>
       <c r="C137" t="n">
-        <v>0.315028</v>
+        <v>0.32</v>
       </c>
       <c r="D137" t="n">
-        <v>0.333594</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="138">
@@ -4832,13 +4832,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.35253</v>
+        <v>0.35</v>
       </c>
       <c r="C138" t="n">
-        <v>0.325779</v>
+        <v>0.33</v>
       </c>
       <c r="D138" t="n">
-        <v>0.321691</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="139">
@@ -4848,13 +4848,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.347395</v>
+        <v>0.35</v>
       </c>
       <c r="C139" t="n">
-        <v>0.321983</v>
+        <v>0.32</v>
       </c>
       <c r="D139" t="n">
-        <v>0.330622</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="140">
@@ -4864,13 +4864,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.335774</v>
+        <v>0.34</v>
       </c>
       <c r="C140" t="n">
-        <v>0.336097</v>
+        <v>0.34</v>
       </c>
       <c r="D140" t="n">
-        <v>0.328129</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="141">
@@ -4880,13 +4880,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.343058</v>
+        <v>0.34</v>
       </c>
       <c r="C141" t="n">
-        <v>0.330208</v>
+        <v>0.33</v>
       </c>
       <c r="D141" t="n">
-        <v>0.326734</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="142">
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.326996</v>
+        <v>0.33</v>
       </c>
       <c r="C142" t="n">
-        <v>0.328359</v>
+        <v>0.33</v>
       </c>
       <c r="D142" t="n">
-        <v>0.344645</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="145">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.312177</v>
+        <v>0.31</v>
       </c>
       <c r="C147" t="n">
-        <v>0.314837</v>
+        <v>0.31</v>
       </c>
       <c r="D147" t="n">
-        <v>0.372986</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="148">
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.315541</v>
+        <v>0.32</v>
       </c>
       <c r="C148" t="n">
-        <v>0.311295</v>
+        <v>0.31</v>
       </c>
       <c r="D148" t="n">
-        <v>0.373165</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="149">
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.314933</v>
+        <v>0.31</v>
       </c>
       <c r="C149" t="n">
-        <v>0.306486</v>
+        <v>0.31</v>
       </c>
       <c r="D149" t="n">
-        <v>0.378582</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="150">
@@ -4967,13 +4967,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.318958</v>
+        <v>0.32</v>
       </c>
       <c r="C150" t="n">
-        <v>0.314477</v>
+        <v>0.31</v>
       </c>
       <c r="D150" t="n">
-        <v>0.366565</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="151">
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.320551</v>
+        <v>0.32</v>
       </c>
       <c r="C151" t="n">
-        <v>0.306011</v>
+        <v>0.31</v>
       </c>
       <c r="D151" t="n">
-        <v>0.373437</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="152">
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.321012</v>
+        <v>0.32</v>
       </c>
       <c r="C152" t="n">
-        <v>0.310311</v>
+        <v>0.31</v>
       </c>
       <c r="D152" t="n">
-        <v>0.368676</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="153">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.318958</v>
+        <v>0.32</v>
       </c>
       <c r="C153" t="n">
-        <v>0.308793</v>
+        <v>0.31</v>
       </c>
       <c r="D153" t="n">
-        <v>0.372249</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="154">
@@ -5031,13 +5031,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.31431</v>
+        <v>0.31</v>
       </c>
       <c r="C154" t="n">
-        <v>0.314439</v>
+        <v>0.31</v>
       </c>
       <c r="D154" t="n">
-        <v>0.371252</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="155">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.317223</v>
+        <v>0.32</v>
       </c>
       <c r="C155" t="n">
-        <v>0.312083</v>
+        <v>0.31</v>
       </c>
       <c r="D155" t="n">
-        <v>0.370693</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="156">
@@ -5063,13 +5063,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.310798</v>
+        <v>0.31</v>
       </c>
       <c r="C156" t="n">
-        <v>0.311344</v>
+        <v>0.31</v>
       </c>
       <c r="D156" t="n">
-        <v>0.377858</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="159">
@@ -5153,49 +5153,49 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5.228</v>
+        <v>5.23</v>
       </c>
       <c r="D162" t="n">
-        <v>10.745</v>
+        <v>10.75</v>
       </c>
       <c r="E162" t="n">
-        <v>14.771</v>
+        <v>14.78</v>
       </c>
       <c r="F162" t="n">
-        <v>20.014</v>
+        <v>20.02</v>
       </c>
       <c r="G162" t="n">
-        <v>6.782</v>
+        <v>6.77</v>
       </c>
       <c r="H162" t="n">
-        <v>10.745</v>
+        <v>10.74</v>
       </c>
       <c r="I162" t="n">
-        <v>14.771</v>
+        <v>14.78</v>
       </c>
       <c r="J162" t="n">
-        <v>18.272</v>
+        <v>18.27</v>
       </c>
       <c r="K162" t="n">
-        <v>9.641999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="L162" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="M162" t="n">
-        <v>9.952</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N162" t="n">
-        <v>15.471</v>
+        <v>15.48</v>
       </c>
       <c r="O162" t="n">
-        <v>12.731</v>
+        <v>12.74</v>
       </c>
       <c r="P162" t="n">
-        <v>12.712</v>
+        <v>12.71</v>
       </c>
       <c r="Q162" t="n">
-        <v>12.721</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="163">
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5.328</v>
+        <v>5.31</v>
       </c>
       <c r="D163" t="n">
         <v>10</v>
       </c>
       <c r="E163" t="n">
-        <v>14.928</v>
+        <v>14.93</v>
       </c>
       <c r="F163" t="n">
-        <v>21.734</v>
+        <v>21.74</v>
       </c>
       <c r="G163" t="n">
         <v>6.76</v>
@@ -5226,31 +5226,31 @@
         <v>10</v>
       </c>
       <c r="I163" t="n">
-        <v>14.928</v>
+        <v>14.93</v>
       </c>
       <c r="J163" t="n">
-        <v>19.42</v>
+        <v>19.43</v>
       </c>
       <c r="K163" t="n">
-        <v>9.066000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="L163" t="n">
-        <v>16.289</v>
+        <v>16.29</v>
       </c>
       <c r="M163" t="n">
-        <v>9.352</v>
+        <v>9.35</v>
       </c>
       <c r="N163" t="n">
-        <v>15.826</v>
+        <v>15.83</v>
       </c>
       <c r="O163" t="n">
-        <v>12.678</v>
+        <v>12.68</v>
       </c>
       <c r="P163" t="n">
-        <v>12.589</v>
+        <v>12.59</v>
       </c>
       <c r="Q163" t="n">
-        <v>12.634</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="164">
@@ -5263,49 +5263,49 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4.649</v>
+        <v>4.64</v>
       </c>
       <c r="D164" t="n">
-        <v>9.738</v>
+        <v>9.74</v>
       </c>
       <c r="E164" t="n">
-        <v>14.107</v>
+        <v>14.11</v>
       </c>
       <c r="F164" t="n">
-        <v>19.601</v>
+        <v>19.6</v>
       </c>
       <c r="G164" t="n">
-        <v>6.024</v>
+        <v>6.02</v>
       </c>
       <c r="H164" t="n">
-        <v>9.738</v>
+        <v>9.74</v>
       </c>
       <c r="I164" t="n">
-        <v>14.107</v>
+        <v>14.11</v>
       </c>
       <c r="J164" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="K164" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="L164" t="n">
-        <v>15.206</v>
+        <v>15.21</v>
       </c>
       <c r="M164" t="n">
-        <v>8.994999999999999</v>
+        <v>9</v>
       </c>
       <c r="N164" t="n">
-        <v>14.842</v>
+        <v>14.85</v>
       </c>
       <c r="O164" t="n">
-        <v>11.963</v>
+        <v>11.96</v>
       </c>
       <c r="P164" t="n">
-        <v>11.918</v>
+        <v>11.93</v>
       </c>
       <c r="Q164" t="n">
-        <v>11.941</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="165">
@@ -5321,46 +5321,46 @@
         <v>4.62</v>
       </c>
       <c r="D165" t="n">
-        <v>9.413</v>
+        <v>9.41</v>
       </c>
       <c r="E165" t="n">
-        <v>14.154</v>
+        <v>14.15</v>
       </c>
       <c r="F165" t="n">
         <v>20.31</v>
       </c>
       <c r="G165" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
       <c r="H165" t="n">
-        <v>9.413</v>
+        <v>9.41</v>
       </c>
       <c r="I165" t="n">
-        <v>14.154</v>
+        <v>14.15</v>
       </c>
       <c r="J165" t="n">
-        <v>18.246</v>
+        <v>18.25</v>
       </c>
       <c r="K165" t="n">
-        <v>8.454000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L165" t="n">
-        <v>15.385</v>
+        <v>15.38</v>
       </c>
       <c r="M165" t="n">
-        <v>8.728</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N165" t="n">
-        <v>14.972</v>
+        <v>14.97</v>
       </c>
       <c r="O165" t="n">
-        <v>11.919</v>
+        <v>11.91</v>
       </c>
       <c r="P165" t="n">
         <v>11.85</v>
       </c>
       <c r="Q165" t="n">
-        <v>11.884</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="166">
@@ -5373,49 +5373,49 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4.539</v>
+        <v>4.55</v>
       </c>
       <c r="D166" t="n">
-        <v>9.301</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E166" t="n">
-        <v>13.795</v>
+        <v>13.79</v>
       </c>
       <c r="F166" t="n">
-        <v>19.447</v>
+        <v>19.45</v>
       </c>
       <c r="G166" t="n">
-        <v>5.817</v>
+        <v>5.81</v>
       </c>
       <c r="H166" t="n">
-        <v>9.301</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>13.795</v>
+        <v>13.79</v>
       </c>
       <c r="J166" t="n">
-        <v>17.571</v>
+        <v>17.57</v>
       </c>
       <c r="K166" t="n">
-        <v>8.349</v>
+        <v>8.35</v>
       </c>
       <c r="L166" t="n">
-        <v>14.925</v>
+        <v>14.92</v>
       </c>
       <c r="M166" t="n">
-        <v>8.603999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="N166" t="n">
         <v>14.55</v>
       </c>
       <c r="O166" t="n">
-        <v>11.637</v>
+        <v>11.63</v>
       </c>
       <c r="P166" t="n">
-        <v>11.577</v>
+        <v>11.57</v>
       </c>
       <c r="Q166" t="n">
-        <v>11.607</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="167">
@@ -5428,49 +5428,49 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3.939</v>
+        <v>3.93</v>
       </c>
       <c r="D167" t="n">
-        <v>8.726000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="E167" t="n">
-        <v>13.366</v>
+        <v>13.37</v>
       </c>
       <c r="F167" t="n">
-        <v>19.075</v>
+        <v>19.08</v>
       </c>
       <c r="G167" t="n">
-        <v>5.224</v>
+        <v>5.22</v>
       </c>
       <c r="H167" t="n">
-        <v>8.726000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="I167" t="n">
-        <v>13.366</v>
+        <v>13.37</v>
       </c>
       <c r="J167" t="n">
-        <v>17.184</v>
+        <v>17.18</v>
       </c>
       <c r="K167" t="n">
-        <v>7.769</v>
+        <v>7.77</v>
       </c>
       <c r="L167" t="n">
-        <v>14.508</v>
+        <v>14.51</v>
       </c>
       <c r="M167" t="n">
-        <v>8.026</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N167" t="n">
         <v>14.13</v>
       </c>
       <c r="O167" t="n">
-        <v>11.139</v>
+        <v>11.14</v>
       </c>
       <c r="P167" t="n">
-        <v>11.078</v>
+        <v>11.08</v>
       </c>
       <c r="Q167" t="n">
-        <v>11.108</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="168">
@@ -5483,49 +5483,49 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4.149</v>
+        <v>4.16</v>
       </c>
       <c r="D168" t="n">
-        <v>8.794</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E168" t="n">
-        <v>13.184</v>
+        <v>13.19</v>
       </c>
       <c r="F168" t="n">
-        <v>18.465</v>
+        <v>18.47</v>
       </c>
       <c r="G168" t="n">
-        <v>5.307</v>
+        <v>5.31</v>
       </c>
       <c r="H168" t="n">
-        <v>8.794</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>13.184</v>
+        <v>13.19</v>
       </c>
       <c r="J168" t="n">
         <v>16.73</v>
       </c>
       <c r="K168" t="n">
-        <v>7.865</v>
+        <v>7.86</v>
       </c>
       <c r="L168" t="n">
-        <v>14.24</v>
+        <v>14.25</v>
       </c>
       <c r="M168" t="n">
-        <v>8.097</v>
+        <v>8.09</v>
       </c>
       <c r="N168" t="n">
-        <v>13.893</v>
+        <v>13.9</v>
       </c>
       <c r="O168" t="n">
-        <v>11.053</v>
+        <v>11.05</v>
       </c>
       <c r="P168" t="n">
-        <v>10.995</v>
+        <v>10.99</v>
       </c>
       <c r="Q168" t="n">
-        <v>11.024</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="169">
@@ -5538,49 +5538,49 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3.848</v>
+        <v>3.84</v>
       </c>
       <c r="D169" t="n">
-        <v>8.619</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E169" t="n">
-        <v>13.153</v>
+        <v>13.14</v>
       </c>
       <c r="F169" t="n">
-        <v>18.622</v>
+        <v>18.62</v>
       </c>
       <c r="G169" t="n">
-        <v>5.107</v>
+        <v>5.11</v>
       </c>
       <c r="H169" t="n">
-        <v>8.619</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>13.153</v>
+        <v>13.14</v>
       </c>
       <c r="J169" t="n">
-        <v>16.818</v>
+        <v>16.81</v>
       </c>
       <c r="K169" t="n">
-        <v>7.665</v>
+        <v>7.66</v>
       </c>
       <c r="L169" t="n">
-        <v>14.247</v>
+        <v>14.24</v>
       </c>
       <c r="M169" t="n">
-        <v>7.917</v>
+        <v>7.92</v>
       </c>
       <c r="N169" t="n">
-        <v>13.886</v>
+        <v>13.87</v>
       </c>
       <c r="O169" t="n">
-        <v>10.956</v>
+        <v>10.95</v>
       </c>
       <c r="P169" t="n">
-        <v>10.901</v>
+        <v>10.89</v>
       </c>
       <c r="Q169" t="n">
-        <v>10.928</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="170">
@@ -5593,49 +5593,49 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3.776</v>
+        <v>3.78</v>
       </c>
       <c r="D170" t="n">
-        <v>8.234</v>
+        <v>8.23</v>
       </c>
       <c r="E170" t="n">
-        <v>12.577</v>
+        <v>12.59</v>
       </c>
       <c r="F170" t="n">
-        <v>17.669</v>
+        <v>17.67</v>
       </c>
       <c r="G170" t="n">
-        <v>4.838</v>
+        <v>4.84</v>
       </c>
       <c r="H170" t="n">
-        <v>8.234</v>
+        <v>8.23</v>
       </c>
       <c r="I170" t="n">
-        <v>12.577</v>
+        <v>12.59</v>
       </c>
       <c r="J170" t="n">
-        <v>16.005</v>
+        <v>16</v>
       </c>
       <c r="K170" t="n">
-        <v>7.342</v>
+        <v>7.34</v>
       </c>
       <c r="L170" t="n">
-        <v>13.595</v>
+        <v>13.61</v>
       </c>
       <c r="M170" t="n">
-        <v>7.555</v>
+        <v>7.55</v>
       </c>
       <c r="N170" t="n">
-        <v>13.263</v>
+        <v>13.27</v>
       </c>
       <c r="O170" t="n">
-        <v>10.469</v>
+        <v>10.47</v>
       </c>
       <c r="P170" t="n">
-        <v>10.409</v>
+        <v>10.41</v>
       </c>
       <c r="Q170" t="n">
-        <v>10.439</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="171">
@@ -5654,40 +5654,40 @@
         <v>4.49</v>
       </c>
       <c r="E171" t="n">
-        <v>9.452999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F171" t="n">
-        <v>14.461</v>
+        <v>14.46</v>
       </c>
       <c r="G171" t="n">
-        <v>1.568</v>
+        <v>1.56</v>
       </c>
       <c r="H171" t="n">
         <v>4.49</v>
       </c>
       <c r="I171" t="n">
-        <v>9.452999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>12.866</v>
+        <v>12.87</v>
       </c>
       <c r="K171" t="n">
-        <v>3.782</v>
+        <v>3.78</v>
       </c>
       <c r="L171" t="n">
-        <v>10.455</v>
+        <v>10.45</v>
       </c>
       <c r="M171" t="n">
-        <v>3.906</v>
+        <v>3.9</v>
       </c>
       <c r="N171" t="n">
-        <v>10.136</v>
+        <v>10.13</v>
       </c>
       <c r="O171" t="n">
-        <v>7.119</v>
+        <v>7.12</v>
       </c>
       <c r="P171" t="n">
-        <v>7.021</v>
+        <v>7.01</v>
       </c>
       <c r="Q171" t="n">
         <v>7.07</v>
